--- a/example data/group/Stats Multiple Comparison - Version 2.xlsx
+++ b/example data/group/Stats Multiple Comparison - Version 2.xlsx
@@ -437,62 +437,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>q | 5mm &amp; 12mm</t>
+          <t>q | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>q | 5mm &amp; 25mm</t>
+          <t>q | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>q | 12mm &amp; 25mm</t>
+          <t>q | 12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>p | 5mm &amp; 12mm</t>
+          <t>p | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>p | 5mm &amp; 25mm</t>
+          <t>p | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p | 12mm &amp; 25mm</t>
+          <t>p | 12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>CI low | 5mm &amp; 12mm</t>
+          <t>CI low | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CI low | 5mm &amp; 25mm</t>
+          <t>CI low | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>CI low | 12mm &amp; 25mm</t>
+          <t>CI low | 12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CI high | 5mm &amp; 12mm</t>
+          <t>CI high | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CI high | 5mm &amp; 25mm</t>
+          <t>CI high | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CI high | 12mm &amp; 25mm</t>
+          <t>CI high | 12 mm &amp; 25 mm</t>
         </is>
       </c>
     </row>
@@ -1543,62 +1543,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>q | 5mm &amp; 12mm</t>
+          <t>q | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>q | 5mm &amp; 25mm</t>
+          <t>q | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>q | 12mm &amp; 25mm</t>
+          <t>q | 12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>p | 5mm &amp; 12mm</t>
+          <t>p | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>p | 5mm &amp; 25mm</t>
+          <t>p | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p | 12mm &amp; 25mm</t>
+          <t>p | 12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>CI low | 5mm &amp; 12mm</t>
+          <t>CI low | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CI low | 5mm &amp; 25mm</t>
+          <t>CI low | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>CI low | 12mm &amp; 25mm</t>
+          <t>CI low | 12 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CI high | 5mm &amp; 12mm</t>
+          <t>CI high | 5 mm &amp; 12 mm</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CI high | 5mm &amp; 25mm</t>
+          <t>CI high | 5 mm &amp; 25 mm</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CI high | 12mm &amp; 25mm</t>
+          <t>CI high | 12 mm &amp; 25 mm</t>
         </is>
       </c>
     </row>
